--- a/research/traditional_assets/database/data/vietnam/vietnam_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_beverage_soft.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.002476780185758514</v>
+        <v>-0.1180616740088106</v>
       </c>
       <c r="H2">
-        <v>0.002476780185758514</v>
+        <v>-0.1180616740088106</v>
       </c>
       <c r="I2">
-        <v>-0.1428792569659443</v>
+        <v>-0.1850220264317181</v>
       </c>
       <c r="J2">
-        <v>-0.1428792569659443</v>
+        <v>-0.1850220264317181</v>
       </c>
       <c r="K2">
-        <v>-1.39</v>
+        <v>-1.64</v>
       </c>
       <c r="L2">
-        <v>-0.2151702786377709</v>
+        <v>-0.2408223201174743</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.6</v>
+        <v>0.367</v>
       </c>
       <c r="V2">
-        <v>0.3286978508217446</v>
+        <v>0.05006821282401092</v>
       </c>
       <c r="W2">
-        <v>-0.1668667466986795</v>
+        <v>-0.2342857142857143</v>
       </c>
       <c r="X2">
-        <v>0.1260129270864002</v>
+        <v>0.2585200442040038</v>
       </c>
       <c r="Y2">
-        <v>-0.2928796737850797</v>
+        <v>-0.492805758489718</v>
       </c>
       <c r="Z2">
-        <v>1.015723270440251</v>
+        <v>0.5541090317331163</v>
       </c>
       <c r="AA2">
-        <v>-0.145125786163522</v>
+        <v>-0.1025223759153784</v>
       </c>
       <c r="AB2">
-        <v>0.08464844799684854</v>
+        <v>0.1402407850185077</v>
       </c>
       <c r="AC2">
-        <v>-0.2297742341603705</v>
+        <v>-0.2427631609338861</v>
       </c>
       <c r="AD2">
-        <v>7.89</v>
+        <v>13.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.89</v>
+        <v>13.6</v>
       </c>
       <c r="AG2">
-        <v>5.289999999999999</v>
+        <v>13.233</v>
       </c>
       <c r="AH2">
-        <v>0.4993670886075949</v>
+        <v>0.6497849976110845</v>
       </c>
       <c r="AI2">
-        <v>0.5298858294157152</v>
+        <v>0.7292225201072386</v>
       </c>
       <c r="AJ2">
-        <v>0.4007575757575757</v>
+        <v>0.6435345037202742</v>
       </c>
       <c r="AK2">
-        <v>0.4304312449145646</v>
+        <v>0.7237871246513154</v>
       </c>
       <c r="AL2">
-        <v>0.596</v>
+        <v>0.618</v>
       </c>
       <c r="AM2">
-        <v>0.4289999999999999</v>
+        <v>0.5489999999999999</v>
       </c>
       <c r="AN2">
-        <v>-12.48417721518987</v>
+        <v>-4.108761329305135</v>
       </c>
       <c r="AO2">
-        <v>-1.548657718120805</v>
+        <v>-2.038834951456311</v>
       </c>
       <c r="AP2">
-        <v>-8.37025316455696</v>
+        <v>-3.997885196374622</v>
       </c>
       <c r="AQ2">
-        <v>-2.151515151515152</v>
+        <v>-2.295081967213115</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.002476780185758514</v>
+        <v>-0.1180616740088106</v>
       </c>
       <c r="H3">
-        <v>0.002476780185758514</v>
+        <v>-0.1180616740088106</v>
       </c>
       <c r="I3">
-        <v>-0.1428792569659443</v>
+        <v>-0.1850220264317181</v>
       </c>
       <c r="J3">
-        <v>-0.1428792569659443</v>
+        <v>-0.1850220264317181</v>
       </c>
       <c r="K3">
-        <v>-1.39</v>
+        <v>-1.64</v>
       </c>
       <c r="L3">
-        <v>-0.2151702786377709</v>
+        <v>-0.2408223201174743</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>0.367</v>
       </c>
       <c r="V3">
-        <v>0.3286978508217446</v>
+        <v>0.05006821282401092</v>
       </c>
       <c r="W3">
-        <v>-0.1668667466986795</v>
+        <v>-0.2342857142857143</v>
       </c>
       <c r="X3">
-        <v>0.1260129270864002</v>
+        <v>0.2585200442040038</v>
       </c>
       <c r="Y3">
-        <v>-0.2928796737850797</v>
+        <v>-0.492805758489718</v>
       </c>
       <c r="Z3">
-        <v>1.015723270440251</v>
+        <v>0.5541090317331163</v>
       </c>
       <c r="AA3">
-        <v>-0.145125786163522</v>
+        <v>-0.1025223759153784</v>
       </c>
       <c r="AB3">
-        <v>0.08464844799684854</v>
+        <v>0.1402407850185077</v>
       </c>
       <c r="AC3">
-        <v>-0.2297742341603705</v>
+        <v>-0.2427631609338861</v>
       </c>
       <c r="AD3">
-        <v>7.89</v>
+        <v>13.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.89</v>
+        <v>13.6</v>
       </c>
       <c r="AG3">
-        <v>5.289999999999999</v>
+        <v>13.233</v>
       </c>
       <c r="AH3">
-        <v>0.4993670886075949</v>
+        <v>0.6497849976110845</v>
       </c>
       <c r="AI3">
-        <v>0.5298858294157152</v>
+        <v>0.7292225201072386</v>
       </c>
       <c r="AJ3">
-        <v>0.4007575757575757</v>
+        <v>0.6435345037202742</v>
       </c>
       <c r="AK3">
-        <v>0.4304312449145646</v>
+        <v>0.7237871246513154</v>
       </c>
       <c r="AL3">
-        <v>0.596</v>
+        <v>0.618</v>
       </c>
       <c r="AM3">
-        <v>0.4289999999999999</v>
+        <v>0.5489999999999999</v>
       </c>
       <c r="AN3">
-        <v>-12.48417721518987</v>
+        <v>-4.108761329305135</v>
       </c>
       <c r="AO3">
-        <v>-1.548657718120805</v>
+        <v>-2.038834951456311</v>
       </c>
       <c r="AP3">
-        <v>-8.37025316455696</v>
+        <v>-3.997885196374622</v>
       </c>
       <c r="AQ3">
-        <v>-2.151515151515152</v>
+        <v>-2.295081967213115</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/vietnam/vietnam_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_beverage_soft.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.1180616740088106</v>
+        <v>-0.199288256227758</v>
       </c>
       <c r="H2">
-        <v>-0.1180616740088106</v>
+        <v>-0.199288256227758</v>
       </c>
       <c r="I2">
-        <v>-0.1850220264317181</v>
+        <v>-0.5</v>
       </c>
       <c r="J2">
-        <v>-0.1850220264317181</v>
+        <v>-0.5</v>
       </c>
       <c r="K2">
-        <v>-1.64</v>
+        <v>-3.56</v>
       </c>
       <c r="L2">
-        <v>-0.2408223201174743</v>
+        <v>-0.6334519572953736</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.367</v>
+        <v>0.277</v>
       </c>
       <c r="V2">
-        <v>0.05006821282401092</v>
+        <v>0.05316698656429943</v>
       </c>
       <c r="W2">
-        <v>-0.2342857142857143</v>
+        <v>-0.5807504078303426</v>
       </c>
       <c r="X2">
-        <v>0.2585200442040038</v>
+        <v>0.2611172965195809</v>
       </c>
       <c r="Y2">
-        <v>-0.492805758489718</v>
+        <v>-0.8418677043499235</v>
       </c>
       <c r="Z2">
-        <v>0.5541090317331163</v>
+        <v>0.349611197511664</v>
       </c>
       <c r="AA2">
-        <v>-0.1025223759153784</v>
+        <v>-0.174805598755832</v>
       </c>
       <c r="AB2">
-        <v>0.1402407850185077</v>
+        <v>0.1121581472568958</v>
       </c>
       <c r="AC2">
-        <v>-0.2427631609338861</v>
+        <v>-0.2869637460127278</v>
       </c>
       <c r="AD2">
-        <v>13.6</v>
+        <v>18</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13.6</v>
+        <v>18</v>
       </c>
       <c r="AG2">
-        <v>13.233</v>
+        <v>17.723</v>
       </c>
       <c r="AH2">
-        <v>0.6497849976110845</v>
+        <v>0.7755277897457992</v>
       </c>
       <c r="AI2">
-        <v>0.7292225201072386</v>
+        <v>0.9278350515463918</v>
       </c>
       <c r="AJ2">
-        <v>0.6435345037202742</v>
+        <v>0.7728164653556011</v>
       </c>
       <c r="AK2">
-        <v>0.7237871246513154</v>
+        <v>0.9267897296449302</v>
       </c>
       <c r="AL2">
-        <v>0.618</v>
+        <v>0.706</v>
       </c>
       <c r="AM2">
-        <v>0.5489999999999999</v>
+        <v>0.6479999999999999</v>
       </c>
       <c r="AN2">
-        <v>-4.108761329305135</v>
+        <v>-7.692307692307693</v>
       </c>
       <c r="AO2">
-        <v>-2.038834951456311</v>
+        <v>-3.980169971671388</v>
       </c>
       <c r="AP2">
-        <v>-3.997885196374622</v>
+        <v>-7.573931623931624</v>
       </c>
       <c r="AQ2">
-        <v>-2.295081967213115</v>
+        <v>-4.33641975308642</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.1180616740088106</v>
+        <v>-0.199288256227758</v>
       </c>
       <c r="H3">
-        <v>-0.1180616740088106</v>
+        <v>-0.199288256227758</v>
       </c>
       <c r="I3">
-        <v>-0.1850220264317181</v>
+        <v>-0.5</v>
       </c>
       <c r="J3">
-        <v>-0.1850220264317181</v>
+        <v>-0.5</v>
       </c>
       <c r="K3">
-        <v>-1.64</v>
+        <v>-3.56</v>
       </c>
       <c r="L3">
-        <v>-0.2408223201174743</v>
+        <v>-0.6334519572953736</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.367</v>
+        <v>0.277</v>
       </c>
       <c r="V3">
-        <v>0.05006821282401092</v>
+        <v>0.05316698656429943</v>
       </c>
       <c r="W3">
-        <v>-0.2342857142857143</v>
+        <v>-0.5807504078303426</v>
       </c>
       <c r="X3">
-        <v>0.2585200442040038</v>
+        <v>0.2611172965195809</v>
       </c>
       <c r="Y3">
-        <v>-0.492805758489718</v>
+        <v>-0.8418677043499235</v>
       </c>
       <c r="Z3">
-        <v>0.5541090317331163</v>
+        <v>0.349611197511664</v>
       </c>
       <c r="AA3">
-        <v>-0.1025223759153784</v>
+        <v>-0.174805598755832</v>
       </c>
       <c r="AB3">
-        <v>0.1402407850185077</v>
+        <v>0.1121581472568958</v>
       </c>
       <c r="AC3">
-        <v>-0.2427631609338861</v>
+        <v>-0.2869637460127278</v>
       </c>
       <c r="AD3">
-        <v>13.6</v>
+        <v>18</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13.6</v>
+        <v>18</v>
       </c>
       <c r="AG3">
-        <v>13.233</v>
+        <v>17.723</v>
       </c>
       <c r="AH3">
-        <v>0.6497849976110845</v>
+        <v>0.7755277897457992</v>
       </c>
       <c r="AI3">
-        <v>0.7292225201072386</v>
+        <v>0.9278350515463918</v>
       </c>
       <c r="AJ3">
-        <v>0.6435345037202742</v>
+        <v>0.7728164653556011</v>
       </c>
       <c r="AK3">
-        <v>0.7237871246513154</v>
+        <v>0.9267897296449302</v>
       </c>
       <c r="AL3">
-        <v>0.618</v>
+        <v>0.706</v>
       </c>
       <c r="AM3">
-        <v>0.5489999999999999</v>
+        <v>0.6479999999999999</v>
       </c>
       <c r="AN3">
-        <v>-4.108761329305135</v>
+        <v>-7.692307692307693</v>
       </c>
       <c r="AO3">
-        <v>-2.038834951456311</v>
+        <v>-3.980169971671388</v>
       </c>
       <c r="AP3">
-        <v>-3.997885196374622</v>
+        <v>-7.573931623931624</v>
       </c>
       <c r="AQ3">
-        <v>-2.295081967213115</v>
+        <v>-4.33641975308642</v>
       </c>
     </row>
   </sheetData>
